--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Questions'!$A$2:$J$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Answer options'!$A$2:$I$261</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Constraints and order'!$A$2:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, risk flags'!$A$2:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Report, risk section'!$A$2:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Report, don''t do yet'!$A$2:$C$36</definedName>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>How do you get paid on a typical job?</t>
+          <t>How do you usually get paid?</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>in full before you start | on a deposit and a balance at the end | in progress payments | on a deposit, with the balance on terms | with nothing upfront | with nothing upfront and the rest on terms</t>
+          <t>in full before you start | with some upfront and the rest at the end | in progress payments | with some upfront and the rest on terms | with nothing upfront, paid at the end | with nothing upfront and the rest on terms</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Once you've invoiced the balance, how long until it's actually in the account?</t>
+          <t>Once you've asked for the balance, how long until it's actually in the account?</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Once you've invoiced the balance, how long until it's actually in the account?</t>
+          <t>Once you've asked for the balance, how long until it's actually in the account?</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>How far ahead is a typical job actually ready?</t>
+          <t>How far ahead is the work actually ready?</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Of the people who enquire and get a quote or a proposal, how many go ahead?</t>
+          <t>Of the people who enquire and find out what it costs, how many go ahead?</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Of the people who enquire and get a quote or a proposal, how many go ahead?</t>
+          <t>Of the people who enquire and find out what it costs, how many go ahead?</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>When a prospect gets your quote, how often do they come back asking what's included, or why it costs what it does?</t>
+          <t>When somebody sees your price, how often do they come back asking what's included, or why it costs what it does?</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>rarely | sometimes | often | on most quotes</t>
+          <t>rarely | sometimes | often | almost every time</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>from a price list they can see themselves | from standard pricing you walk them through | from a quote built from scratch every time | from a number that depends who's asking</t>
+          <t>from a price list they can see themselves | from standard pricing you walk them through | from a price worked out from scratch every time | from a number that depends who's asking</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>On a typical job or sale, what's left after the direct cost of delivering it?</t>
+          <t>On a typical sale, what's left after the direct cost of delivering it?</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>On a typical job or sale, what's left after the direct cost of delivering it?</t>
+          <t>On a typical sale, what's left after the direct cost of delivering it?</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>How often does a job end up costing more to deliver than you quoted?</t>
+          <t>How often does something end up costing more to deliver than you priced it at?</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>rarely | sometimes | often | on most jobs</t>
+          <t>rarely | sometimes | often | most of the time</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>constraintDef / talent / open [2]</t>
+          <t>constraintDef / talent / open [3]</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>How do you get paid on a typical job?</t>
+          <t>How do you usually get paid?</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Once you've invoiced the balance, how long until it's actually in the account?</t>
+          <t>Once you've asked for the balance, how long until it's actually in the account?</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>On paper, meaning the accountant's version, not what's in the bank.</t>
+          <t>Materials, wages, anything you'd have to pay for before the customer pays you.</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Capacity meaning the hours, people or stock you'd need to actually do the work.</t>
+          <t>Capacity meaning the hours, people or materials you'd need to actually do the work.</t>
         </is>
       </c>
       <c r="G22" s="5" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>How far ahead is a typical job actually ready?</t>
+          <t>How far ahead is the work actually ready?</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Long hours on an event day or a job site are the job. This is about the weeks in between.</t>
+          <t>Long hours on a delivery day are the work itself. This is about the weeks in between.</t>
         </is>
       </c>
       <c r="G26" s="5" t="n">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Of the people who enquire and get a quote or a proposal, how many go ahead?</t>
+          <t>Of the people who enquire and find out what it costs, how many go ahead?</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>When a prospect gets your quote, how often do they come back asking what's included, or why it costs what it does?</t>
+          <t>When somebody sees your price, how often do they come back asking what's included, or why it costs what it does?</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Has the proportion of quotes that turn into work changed in the last 12 months?</t>
+          <t>Has the proportion of enquiries that turn into work changed in the last 12 months?</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>On a typical job or sale, what's left after the direct cost of delivering it?</t>
+          <t>On a typical sale, what's left after the direct cost of delivering it?</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Direct cost meaning labour, materials, subcontractors, whatever that specific job consumed.</t>
+          <t>Direct cost meaning labour, materials, subcontractors, whatever that specific piece of work consumed.</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>How often does a job end up costing more to deliver than you quoted?</t>
+          <t>How often does something end up costing more to deliver than you priced it at?</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Do you know which customers, jobs or product lines actually make you money?</t>
+          <t>Do you know which customers, products or lines of work actually make you money?</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>more than ten years in</t>
+          <t>one piece of work at a time</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>How do you get paid on a typical job?</t>
+          <t>How do you usually get paid?</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>How do you get paid on a typical job?</t>
+          <t>How do you usually get paid?</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>A deposit upfront, balance on completion</t>
+          <t>Some upfront, the rest when it's done</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>on a deposit and a balance at the end</t>
+          <t>with some upfront and the rest at the end</t>
         </is>
       </c>
       <c r="G34" s="5" t="n">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>How do you get paid on a typical job?</t>
+          <t>How do you usually get paid?</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Progress payments across the job</t>
+          <t>Progress payments along the way</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>How do you get paid on a typical job?</t>
+          <t>How do you usually get paid?</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>A deposit upfront, balance on terms after</t>
+          <t>Some upfront, the rest on terms after</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>on a deposit, with the balance on terms</t>
+          <t>with some upfront and the rest on terms</t>
         </is>
       </c>
       <c r="G36" s="5" t="n">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>How do you get paid on a typical job?</t>
+          <t>How do you usually get paid?</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Nothing upfront, invoiced on completion</t>
+          <t>Nothing upfront, paid when it's done</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>with nothing upfront</t>
+          <t>with nothing upfront, paid at the end</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>How do you get paid on a typical job?</t>
+          <t>How do you usually get paid?</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Nothing upfront, invoiced on terms after</t>
+          <t>Nothing upfront, paid on terms after</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Once you've invoiced the balance, how long until it's actu...</t>
+          <t>Once you've asked for the balance, how long until it's act...</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Straight away, we're paid before we'd invoice</t>
+          <t>Straight away, we're paid before we'd even ask</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Once you've invoiced the balance, how long until it's actu...</t>
+          <t>Once you've asked for the balance, how long until it's act...</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Once you've invoiced the balance, how long until it's actu...</t>
+          <t>Once you've asked for the balance, how long until it's act...</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Once you've invoiced the balance, how long until it's actu...</t>
+          <t>Once you've asked for the balance, how long until it's act...</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Once you've invoiced the balance, how long until it's actu...</t>
+          <t>Once you've asked for the balance, how long until it's act...</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Quoting and pricing jobs</t>
+          <t>Pricing and putting numbers together</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Chasing invoices and doing the books</t>
+          <t>Chasing money and doing the books</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>How far ahead is a typical job actually ready?</t>
+          <t>How far ahead is the work actually ready?</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>How far ahead is a typical job actually ready?</t>
+          <t>How far ahead is the work actually ready?</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>How far ahead is a typical job actually ready?</t>
+          <t>How far ahead is the work actually ready?</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>How far ahead is a typical job actually ready?</t>
+          <t>How far ahead is the work actually ready?</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Of the people who enquire and get a quote or a proposal, h...</t>
+          <t>Of the people who enquire and find out what it costs, how ...</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Of the people who enquire and get a quote or a proposal, h...</t>
+          <t>Of the people who enquire and find out what it costs, how ...</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Of the people who enquire and get a quote or a proposal, h...</t>
+          <t>Of the people who enquire and find out what it costs, how ...</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Of the people who enquire and get a quote or a proposal, h...</t>
+          <t>Of the people who enquire and find out what it costs, how ...</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>When a prospect gets your quote, how often do they come ba...</t>
+          <t>When somebody sees your price, how often do they come back...</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>When a prospect gets your quote, how often do they come ba...</t>
+          <t>When somebody sees your price, how often do they come back...</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>When a prospect gets your quote, how often do they come ba...</t>
+          <t>When somebody sees your price, how often do they come back...</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>When a prospect gets your quote, how often do they come ba...</t>
+          <t>When somebody sees your price, how often do they come back...</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
@@ -9712,12 +9712,12 @@
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>On most quotes</t>
+          <t>Almost every time</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>on most quotes</t>
+          <t>almost every time</t>
         </is>
       </c>
       <c r="G149" s="5" t="n">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Has the proportion of quotes that turn into work changed i...</t>
+          <t>Has the proportion of enquiries that turn into work change...</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Has the proportion of quotes that turn into work changed i...</t>
+          <t>Has the proportion of enquiries that turn into work change...</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Has the proportion of quotes that turn into work changed i...</t>
+          <t>Has the proportion of enquiries that turn into work change...</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Has the proportion of quotes that turn into work changed i...</t>
+          <t>Has the proportion of enquiries that turn into work change...</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>Every job gets quoted from scratch</t>
+          <t>Every price is worked out from scratch</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>from a quote built from scratch every time</t>
+          <t>from a price worked out from scratch every time</t>
         </is>
       </c>
       <c r="G156" s="5" t="n">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>On a typical job or sale, what's left after the direct cos...</t>
+          <t>On a typical sale, what's left after the direct cost of de...</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>On a typical job or sale, what's left after the direct cos...</t>
+          <t>On a typical sale, what's left after the direct cost of de...</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>On a typical job or sale, what's left after the direct cos...</t>
+          <t>On a typical sale, what's left after the direct cost of de...</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>On a typical job or sale, what's left after the direct cos...</t>
+          <t>On a typical sale, what's left after the direct cost of de...</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>How often does a job end up costing more to deliver than y...</t>
+          <t>How often does something end up costing more to deliver th...</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>How often does a job end up costing more to deliver than y...</t>
+          <t>How often does something end up costing more to deliver th...</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>How often does a job end up costing more to deliver than y...</t>
+          <t>How often does something end up costing more to deliver th...</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>How often does a job end up costing more to deliver than y...</t>
+          <t>How often does something end up costing more to deliver th...</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="E197" s="7" t="inlineStr">
         <is>
-          <t>On most jobs</t>
+          <t>Most of the time</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>on most jobs</t>
+          <t>most of the time</t>
         </is>
       </c>
       <c r="G197" s="5" t="n">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>Do you know which customers, jobs or product lines actuall...</t>
+          <t>Do you know which customers, products or lines of work act...</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>Yes, job by job</t>
+          <t>Yes, down to the individual sale</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>Do you know which customers, jobs or product lines actuall...</t>
+          <t>Do you know which customers, products or lines of work act...</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>Do you know which customers, jobs or product lines actuall...</t>
+          <t>Do you know which customers, products or lines of work act...</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>Do you know which customers, jobs or product lines actuall...</t>
+          <t>Do you know which customers, products or lines of work act...</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="E203" s="7" t="inlineStr">
         <is>
-          <t>How many quotes turn into work</t>
+          <t>How many enquiries turn into work</t>
         </is>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
@@ -13870,7 +13870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Being talent constrained means you're missing a layer in the business, not missing extra hands.</t>
+          <t>Double your customers tomorrow and you'd struggle to deliver, because there's a layer of talent missing from the business.</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
@@ -13984,15 +13984,11 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>{d.unownedLayers}</t>
+          <t>Being talent constrained means you're missing a layer, not missing extra hands.</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>{d.unownedLayers}</t>
-        </is>
-      </c>
+      <c r="E6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -14007,13 +14003,13 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Most of last week went to {d.ownerTasks}.</t>
+          <t>{d.unownedLayers}</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>{d.ownerTasks}</t>
+          <t>{d.unownedLayers}</t>
         </is>
       </c>
     </row>
@@ -14025,18 +14021,18 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Opening sentence 4</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>the work that actually moves the business forward got {q56.band}</t>
+          <t>Most of last week went to {d.ownerTasks}.</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>{q56.band}</t>
+          <t>{d.ownerTasks}</t>
         </is>
       </c>
     </row>
@@ -14048,18 +14044,18 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>if you went dark for a month the business {q12.band}</t>
+          <t>the work that actually moves the business forward got {q56.band}</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>{q12.band}</t>
+          <t>{q56.band}</t>
         </is>
       </c>
     </row>
@@ -14071,18 +14067,18 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>{q14.band}</t>
+          <t>if you went dark for a month the business {q12.band}</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>{q14.band}</t>
+          <t>{q12.band}</t>
         </is>
       </c>
     </row>
@@ -14094,16 +14090,20 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Hiring another pair of hands underneath you doesn't touch this. What's missing is a whole role that doesn't exist yet, and until it does, everything you add lands on the same desk.</t>
+          <t>{q14.band}</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>{q14.band}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -14113,12 +14113,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Hire one role that owns a layer of the business, with the authority to run it. Not another pair of hands underneath you.</t>
+          <t>Hiring another pair of hands underneath you doesn't fix this. What's missing is a whole role that doesn't exist yet, and adding it is what unblocks the business.</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
@@ -14132,20 +14132,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Write down every task you did last week.</t>
-        </is>
-      </c>
+          <t>Fix, lead line</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
       <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -14155,12 +14147,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Against each one, write the role that should own it. A role, not a person already in the business.</t>
+          <t>Write down every task you do, in fifteen minute blocks, for a full week.</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
@@ -14178,12 +14170,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Whichever role has the most tasks against it, or the most hours, hire that role first.</t>
+          <t>Against each task, write the role that should own it in an ideal world.</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
@@ -14201,12 +14193,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Give them responsibility and the authority to go with it. One without the other doesn't work.</t>
+          <t>Take whichever role has the most tasks against it, or the most hours in the week.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
@@ -14224,12 +14216,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Train them yourself, then give them ninety days to prove they're the one.</t>
+          <t>Hire that role.</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
@@ -14242,84 +14234,92 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>fulfilment</t>
+          <t>talent</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
+          <t>Train them yourself.</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>fulfilment</t>
+          <t>talent</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
+          <t>Give them the responsibility and the authority to run it. One without the other doesn't work.</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>fulfilment</t>
+          <t>talent</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Fix action 7</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>This is capacity, not capability. You know how to do the work, but you can't do enough of it.</t>
+          <t>Give them ninety days to prove they're the one.</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>fulfilment</t>
+          <t>talent</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Fix action 8</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>you're running {q16.band}</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>you're running at {q16.exact}% booked</t>
-        </is>
-      </c>
+          <t>If they don't work out, hire again and run it the same way. If they do, come back here and find out what's capping you now.</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>{q16.band}, {q16.exact}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -14331,20 +14331,16 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>{q17.band}</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>{q17.band}</t>
-        </is>
-      </c>
+      <c r="E22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -14354,20 +14350,16 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>lead times have {q18.band}</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>{q18.band}</t>
-        </is>
-      </c>
+      <c r="E23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -14377,20 +14369,16 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Opening sentence 1</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>a typical job is ready {q19.band}</t>
+          <t>Double your customers tomorrow and you couldn't deliver, because there isn't enough capacity in the business.</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr"/>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>{q19.band}</t>
-        </is>
-      </c>
+      <c r="E24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -14400,12 +14388,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Opening sentence 2</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Nothing at the front of the business needs attention until the back of it can breathe. Anything you do to bring in more work right now gets paid for by the customers you already have.</t>
+          <t>This is capacity, not capability. You know how to do the work and you can't do enough of it.</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr"/>
@@ -14419,16 +14407,24 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Make what you already have work properly, cut what isn't earning its capacity, then hire. In that order.</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr"/>
-      <c r="E26" s="8" t="inlineStr"/>
+          <t>you're running {q16.band}</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>you're running at {q16.exact}% booked</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>{q16.band}, {q16.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -14438,18 +14434,18 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Find the one step everything stalls at, and put the next day into streamlining that one step.</t>
+          <t>{q17.band}</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>{q17.band}</t>
         </is>
       </c>
     </row>
@@ -14461,18 +14457,18 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Write the five things that go wrong most often into one page checklists. Undocumented work is slow work.</t>
+          <t>lead times have {q18.band}</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>q46 is b/c</t>
+          <t>{q18.band}</t>
         </is>
       </c>
     </row>
@@ -14484,18 +14480,18 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Look at what your best people actually spent last week on. Anything that didn't need them is capacity you already have.</t>
+          <t>the work is typically ready {q19.band}</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr"/>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>{q19.band}</t>
         </is>
       </c>
     </row>
@@ -14507,20 +14503,16 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Cut the jobs that eat the most capacity for the least return.</t>
+          <t>Nothing at the front of the business needs attention until the back of it can breathe. More capacity is what fixes this, and there's work to do before you buy it.</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr"/>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -14530,215 +14522,219 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Then hire more capacity into the roles that need it.</t>
-        </is>
-      </c>
+          <t>Fix, lead line</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr"/>
       <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
+          <t>Write down exactly how what you sell gets delivered, one step at a time.</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr"/>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
+          <t>Write down every other task your delivery people do that isn't that.</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="8" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>You're full and busy, and there's nothing left at the end of it.</t>
+          <t>Find the three things across those two lists that slow delivery down the most.</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>what's left after direct costs sits {q36.band}</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>what's left after direct costs sits at {q36.exact}%</t>
-        </is>
-      </c>
+          <t>Spend one week streamlining those three things and nothing else.</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr"/>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>{q36.band}, {q36.exact}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>after everything it's {q37.band}</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>after everything it's {q37.exact}%</t>
-        </is>
-      </c>
+          <t>Rewrite the first list with what changed, and make it the way it's done from now on.</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>{q37.band}, {q37.exact}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>{q38.band}</t>
+          <t>Cut the bottom ten percent of customers, the ones taking the most time for the least return.</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>{q38.band}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Fix action 7</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>jobs run over what you quoted {q39.band}</t>
+          <t>Now hire more capacity into the roles that need it.</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr"/>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>{q39.band}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Fix action 8</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Volume won't rescue this. At the margin you're running, more work gets you more of the same result and it arrives faster.</t>
+          <t>Run it that way for ninety days.</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
-      <c r="E39" s="8" t="inlineStr"/>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Fix action 9</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>You need to know what each job actually earns you before you change anything. A price rise can cost you customers as easily as it can fix the margin.</t>
+          <t>If delivery still can't keep up, work the list again. If it can, come back here and find out what's capping you now.</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr"/>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -14748,20 +14744,16 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Raise prices on new work now. Ten percent across the board, and watch what actually happens.</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>q38 is c/d</t>
-        </is>
-      </c>
+      <c r="E41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -14771,20 +14763,16 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Work out what each job really costs, your own time included, then rank your last twenty by what was left.</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr"/>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -14794,20 +14782,16 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Opening sentence 1</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Quote a contingency into the jobs that historically run over. You already know which ones they are.</t>
+          <t>Double your customers tomorrow and it wouldn't help, because there isn't enough margin in what you're already doing.</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>q39 is c/d</t>
-        </is>
-      </c>
+      <c r="E43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -14817,20 +14801,16 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Opening sentence 2</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Find your worst three customers by margin, then reprice them or let them go.</t>
+          <t>You're busy, and there's nothing left at the end of it.</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -14840,230 +14820,238 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Don't discount to win. A discount is the fastest way to buy work you'll resent delivering.</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr"/>
+          <t>what's left after direct costs sits {q36.band}</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>what's left after direct costs sits at {q36.exact}%</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>{q36.band}, {q36.exact}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr"/>
-      <c r="E46" s="8" t="inlineStr"/>
+          <t>after everything it's {q37.band}</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>after everything it's {q37.exact}%</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>{q37.band}, {q37.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
+          <t>{q38.band}</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
-      <c r="E47" s="8" t="inlineStr"/>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>{q38.band}</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Value here means what the customer perceives, and it has nothing to do with your pricing or your margin. They buy, then they either stop or start giving most of the work to somebody else.</t>
+          <t>the work runs over what you priced it at {q39.band}</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr"/>
-      <c r="E48" s="8" t="inlineStr"/>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>{q39.band}</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>of the customers you had a year ago, {q21.band} still buy from you</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>of the customers you had a year ago, {q21.exact}% still buy from you</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>{q21.band}, {q21.exact}</t>
-        </is>
-      </c>
+          <t>More volume won't solve this. You need to make more on the work you're already doing, without adding a single customer.</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr"/>
+      <c r="E49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>you get {q57.band} of the work they put out</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>you get {q57.exact}% of the work they put out</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>{q57.band}, {q57.exact}</t>
-        </is>
-      </c>
+          <t>Fix, lead line</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr"/>
+      <c r="D50" s="7" t="inlineStr"/>
+      <c r="E50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>they come back unprompted {q22.band}</t>
+          <t>Work out what each piece of work really costs you, your own time included, and rank the last twenty by what was left.</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>{q22.band}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>referrals bring in {q23.band} of your new customers</t>
+          <t>Take the bottom five. For each one, write down what it was that ate the money.</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr"/>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>{q23.band}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>You're filling a leaky bucket. Every dollar going into finding new customers is currently paying to replace the ones walking out the other side, which is why the business feels busy and stays the same size.</t>
+          <t>Whatever shows up on more than one of them, that's the leak. Fix that before you touch anything else.</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr"/>
-      <c r="E53" s="8" t="inlineStr"/>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>You need to find out why customers leave or shrink, and fix that, before you spend another dollar finding new ones.</t>
+          <t>Put your prices up on everything new. If nobody flinches, they were too low.</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr"/>
-      <c r="E54" s="8" t="inlineStr"/>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>q38 is c/d</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Ring ten customers who stopped buying or cut back, and ask them straight. Not a survey. A phone call.</t>
+          <t>Build the thing that historically runs over into the price, so you stop absorbing it.</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr"/>
@@ -15076,40 +15064,40 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Ask your biggest customers what they give to somebody else, and why. That work already exists, you're just not getting it.</t>
+          <t>Reprice your three worst customers by what's left, or let them go.</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr"/>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>q57 is c/d</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 7</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Look hard at what happens in the first thirty days after somebody buys. That's the part of the experience you control most tightly.</t>
+          <t>Hold the new prices for ninety days without discounting to win anything.</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr"/>
@@ -15122,17 +15110,17 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix action 8</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Build one reason to come back that you initiate. A check in, or the next step offered before they go looking.</t>
+          <t>If there's still nothing left at the end, work the list again. If there is, come back here and find out what's capping you now.</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr"/>
@@ -15150,35 +15138,31 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Measure retention monthly, so a drop shows up while you can still do something about it.</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr"/>
@@ -15187,17 +15171,17 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Opening sentence 1</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
+          <t>Double your customers tomorrow and you'd have no trouble delivering, and you can't keep enough of them to fill what you've got.</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
@@ -15206,17 +15190,17 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Opening sentence 1</t>
+          <t>Opening sentence 2</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Enquiries arrive and they don't convert.</t>
+          <t>They buy, then they either stop or start giving most of the work to somebody else.</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr"/>
@@ -15225,170 +15209,174 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Opening sentence 2</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>That isn't a sales technique problem, it's what's on the table. Either the value in the offer doesn't justify the price you're asking, or there's something in the way of somebody saying yes.</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="8" t="inlineStr"/>
+          <t>of the customers you had a year ago, {q21.band} still buy from you</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>of the customers you had a year ago, {q21.exact}% still buy from you</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>{q21.band}, {q21.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>your close rate sits {q26.band}</t>
+          <t>you get {q57.band} of the work they put out</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>your close rate sits at {q26.exact}%</t>
+          <t>you get {q57.exact}% of the work they put out</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>{q26.band}, {q26.exact}</t>
+          <t>{q57.band}, {q57.exact}</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>the most common reason you lose is {q27.band}</t>
+          <t>they come back unprompted {q22.band}</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr"/>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>{q27.band}</t>
+          <t>{q22.band}</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>prospects come back on your quote asking what's included {q28.band}</t>
+          <t>referrals bring in {q23.band} of your new customers</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr"/>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>{q28.band}</t>
+          <t>{q23.band}</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>they find out what you charge {q30.band}</t>
+          <t>You're filling a leaky bucket. Every dollar going into finding new customers is paying to replace the ones walking out the other side, which is why the business feels busy and stays the same size. Selling to somebody who has already bought is far easier than finding somebody new.</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr"/>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>{q30.band}</t>
-        </is>
-      </c>
+      <c r="E67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>You don't fix this by dropping the price. You fix it by putting things into the offer that cost you very little and are worth real money to the buyer, and by removing whatever a prospect has to get over before they can say yes.</t>
-        </is>
-      </c>
+          <t>Fix, lead line</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr"/>
       <c r="D68" s="7" t="inlineStr"/>
       <c r="E68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>You need more value in the offer than the price is asking for, and the hurdles taken out of the way of somebody saying yes.</t>
+          <t>Write down every point of contact a customer has with you, from the moment they buy through to six months later.</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr"/>
-      <c r="E69" s="8" t="inlineStr"/>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>List everything you already do for a customer that isn't written into the offer. That's value nobody can see.</t>
+          <t>Put as much as you can into the first ninety days. Surprise them. That's the window where they decide what you're worth.</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr"/>
@@ -15401,17 +15389,17 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Add two things that cost you close to nothing and are worth real money to the buyer. A guarantee, or something they would otherwise have to go and source themselves.</t>
+          <t>Find the longest silence on that list and put something in it.</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr"/>
@@ -15424,63 +15412,63 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Write down every question a prospect asks after they get the quote, then answer all of them inside the quote itself.</t>
+          <t>Ring ten customers who stopped or cut back and ask them straight why. Not a survey.</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr"/>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>q28 is c/d</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Put a price or a range where they can see it. Making somebody wait for a number is a hurdle before they have even decided.</t>
+          <t>Whatever more than one of them says, fix that.</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr"/>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>q30 is c/d</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Sort your last twenty losses by reason and count them. If price keeps coming up, look at the value in the offer before you look at the number.</t>
+          <t>Build one reason to come back that you start, rather than waiting to be asked.</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr"/>
@@ -15493,78 +15481,86 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Fix action 6</t>
+          <t>Fix action 7</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Test the new offer on the next ten enquiries before you change anything else.</t>
+          <t>Ask your biggest customers what they give to somebody else, and why.</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr"/>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>q57 is c/d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Fix action 8</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
+          <t>Run all of that for ninety days and measure who came back.</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr"/>
-      <c r="E76" s="8" t="inlineStr"/>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Fix action 9</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
+          <t>If they're still leaving, work the list again. If they're staying, come back here and find out what's capping you now.</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr"/>
-      <c r="E77" s="8" t="inlineStr"/>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>You've got capacity sitting idle and not enough people asking.</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr"/>
@@ -15573,220 +15569,204 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>enquiries run {q31.band}</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>enquiries run at about {q31.exact} a month</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>{q31.band}, {q31.exact}</t>
-        </is>
-      </c>
+          <t>The tightest thing is {c}</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr"/>
+      <c r="E79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Opening sentence 1</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>volume has {q33.band} over the last year</t>
+          <t>Double your customers tomorrow and you'd have no trouble delivering, and you can't close enough of them to fill what you've got.</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr"/>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>{q33.band}</t>
-        </is>
-      </c>
+      <c r="E80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Opening sentence 2</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>{q35.band}</t>
+          <t>People come to you and they don't buy. It's the offer. Either the value in it doesn't justify what you're asking, or there's something in the way of somebody saying yes.</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr"/>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>{q35.band}</t>
-        </is>
-      </c>
+      <c r="E81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>You could take on more work tomorrow, which is what separates this from a delivery problem. Nothing downstream is broken. The business just isn't being fed, and it won't start feeding itself.</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr"/>
-      <c r="E82" s="8" t="inlineStr"/>
+          <t>your close rate sits {q26.band}</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>your close rate sits at {q26.exact}%</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>{q26.band}, {q26.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>You need one lead source running properly and consistently before you go anywhere near a second.</t>
+          <t>the most common reason you lose is {q27.band}</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr"/>
-      <c r="E83" s="8" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>{q27.band}</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Whatever you're doing to generate enquiries isn't running consistently. Start with the one thing you can do every week without fail.</t>
+          <t>people come back asking what's included {q28.band}</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr"/>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>q35 is b/c</t>
+          <t>{q28.band}</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Pick the lead source that already brings your best customers and put real weight behind it.</t>
+          <t>they find out what you charge {q30.band}</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>{q30.band}</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Go and ask for work. Outbound to the twenty businesses you'd most like to work with beats waiting on referrals.</t>
+          <t>You don't fix this by dropping the price. You fix it by putting things into the offer that cost you very little and are worth real money to the buyer, and by clearing whatever somebody has to get over before they can say yes.</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr"/>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E86" s="8" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>Everything arrives through one lead source. Stand up a second before that one changes.</t>
-        </is>
-      </c>
+          <t>Fix, lead line</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr"/>
       <c r="D87" s="7" t="inlineStr"/>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>q43 is c</t>
-        </is>
-      </c>
+      <c r="E87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Ask every happy customer for one introduction.</t>
+          <t>List everything you already do for a customer that isn't written into the offer, and write it in.</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr"/>
@@ -15799,17 +15779,17 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Fix action 6</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Give a lead source ninety days before you judge it. Anything shorter is guesswork.</t>
+          <t>Add two or three things that cost you close to nothing and are worth real money to the buyer. A guarantee, or something they'd otherwise have to go and source themselves.</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr"/>
@@ -15819,8 +15799,513 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 3</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Write down every question somebody asks you after they've seen the price.</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr"/>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 4</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Answer all of them inside the offer, before anybody has to ask.</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 5</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>Shorten the time between somebody making contact and somebody getting a number.</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr"/>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 6</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Make the price and what's in it easier to see.</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr"/>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 7</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>Run the new offer for one month.</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr"/>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 8</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>If the close rate hasn't moved, put more value in and go again. If it has, come back here and find out what's capping you now.</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr"/>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>You are {c} constrained</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr"/>
+      <c r="E96" s="8" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Title, nothing failing</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>The tightest thing is {c}</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr"/>
+      <c r="E97" s="8" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Opening sentence 1</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>Double your customers tomorrow and you'd have no trouble delivering, and you can't find enough of them to fill what you've got.</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr"/>
+      <c r="E98" s="8" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Opening sentence 2</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>You've got capacity sitting idle and not enough people asking.</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr"/>
+      <c r="E99" s="8" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Evidence clause 1</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>enquiries run {q31.band}</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>enquiries run at about {q31.exact} a month</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>{q31.band}, {q31.exact}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Evidence clause 2</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>volume has {q33.band} over the last year</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr"/>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>{q33.band}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Evidence clause 3</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>{q35.band}</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr"/>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>{q35.band}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Nothing downstream is broken. The business needs more people coming in the top, and it won't start feeding itself.</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr"/>
+      <c r="E103" s="8" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Fix, lead line</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr"/>
+      <c r="D104" s="7" t="inlineStr"/>
+      <c r="E104" s="8" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 1</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Ask your happiest customers for something in writing or on camera. Pay for it, or give them something for it.</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr"/>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 2</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Put that where somebody deciding on you will actually see it.</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr"/>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 3</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>Take the source that already brings your best customers and put two or three times the effort into it.</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr"/>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 4</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Stand up a second source that doesn't rely on being found. Going out and asking directly is the usual one.</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr"/>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 5</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>Set up a referral programme with something real in it for the customer who refers.</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr"/>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 6</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>Launch it by asking every customer, one at a time, for a single introduction.</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr"/>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 7</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Run all of that for ninety days without adding anything else.</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr"/>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 8</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>If enquiries haven't moved, work the list again. If they have, come back here and find out what's capping you now.</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr"/>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:E89"/>
+  <autoFilter ref="A2:E112"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -16346,12 +16831,12 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Move to a deposit on every job. Fifty percent thirty days out and the balance the week before, so the money is in before your costs go out.</t>
+          <t>Take money upfront on everything. Half of it well before you start and the rest before you deliver, so it's in the account before your own costs go out.</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Line the deposit up to land before your cost of goods does. On jobs where the number moves on the day, charge the balance afterwards and refund the difference.</t>
+          <t>Line the upfront money up to land before your own costs do. Where the final number can't be known in advance, take the balance afterwards and refund the difference.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
@@ -16622,7 +17107,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Don't promise a shorter lead time to win a job.</t>
+          <t>Don't promise a shorter lead time to win something.</t>
         </is>
       </c>
     </row>
@@ -16690,7 +17175,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Don't take the big thin job because it's good for the brand. Reputation doesn't pay wages.</t>
+          <t>Don't take the big thin one because it's good for the brand. Reputation doesn't pay wages.</t>
         </is>
       </c>
     </row>

--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -1759,7 +1759,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>above 50% | in the 25 to 50% range | in the 10 to 25% range | under 10%</t>
+          <t>above 80% | in the 50 to 80% range | in the 25 to 50% range | under 25%</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>constraintDef / offer / evidence [1] / banded</t>
+          <t>constraintDef / offer / evidence [1] / banded  prompts [1] / text</t>
         </is>
       </c>
     </row>
@@ -9327,19 +9327,23 @@
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>More than half</t>
+          <t>More than 80%</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>above 50%</t>
+          <t>above 80%</t>
         </is>
       </c>
       <c r="G138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H138" s="3" t="inlineStr"/>
-      <c r="I138" s="3" t="inlineStr"/>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>Rules out offer entirely</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
@@ -9362,12 +9366,12 @@
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>25% to 50%</t>
+          <t>50% to 80%</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>in the 25 to 50% range</t>
+          <t>in the 50 to 80% range</t>
         </is>
       </c>
       <c r="G139" s="5" t="n">
@@ -9397,12 +9401,12 @@
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>10% to 25%</t>
+          <t>25% to 50%</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>in the 10 to 25% range</t>
+          <t>in the 25 to 50% range</t>
         </is>
       </c>
       <c r="G140" s="5" t="n">
@@ -9432,12 +9436,12 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>Under 10%</t>
+          <t>Under 25%</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>under 10%</t>
+          <t>under 25%</t>
         </is>
       </c>
       <c r="G141" s="5" t="n">
